--- a/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.21365250454281</v>
+        <v>44.87760629397405</v>
       </c>
       <c r="M2" t="n">
-        <v>100.3514834867991</v>
+        <v>99.94172155283161</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08440203758362</v>
+        <v>87.94722243086923</v>
       </c>
       <c r="C3" t="n">
-        <v>45.95933275948377</v>
+        <v>45.87101057721738</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853754162333</v>
+        <v>2.228568780701174</v>
       </c>
       <c r="E3" t="n">
-        <v>5.726955614829611</v>
+        <v>5.669108698762296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429512513874443</v>
+        <v>0.7428562602337246</v>
       </c>
       <c r="G3" t="n">
-        <v>33.98316911285865</v>
+        <v>33.95392547346946</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17575756382243</v>
+        <v>34.17138797075133</v>
       </c>
       <c r="I3" t="n">
-        <v>6.583269419351621</v>
+        <v>6.538523620490451</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643445321171527</v>
+        <v>4.642851626460779</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91559796241638</v>
+        <v>12.05277756913079</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88877672074179</v>
+        <v>48.84149534224372</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637074426419</v>
+        <v>106.7652834885919</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27566155314969</v>
+        <v>86.91574534563298</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78753222371405</v>
+        <v>42.4711104085541</v>
       </c>
       <c r="D4" t="n">
-        <v>2.19046278528931</v>
+        <v>2.178195062200131</v>
       </c>
       <c r="E4" t="n">
-        <v>6.544574288365006</v>
+        <v>6.450996275960444</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445112249152951</v>
+        <v>0.7444118390088862</v>
       </c>
       <c r="G4" t="n">
-        <v>33.39782483659914</v>
+        <v>33.18644389577824</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24751634610357</v>
+        <v>34.24294459440877</v>
       </c>
       <c r="I4" t="n">
-        <v>5.49757691615677</v>
+        <v>5.460179684470994</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653195155720594</v>
+        <v>4.652573993805539</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72433844685031</v>
+        <v>13.08425465436702</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30526073445364</v>
+        <v>44.26300928095415</v>
       </c>
       <c r="M4" t="n">
-        <v>99.817131405018</v>
+        <v>99.81837434387526</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.27733237373788</v>
+        <v>85.63844000346448</v>
       </c>
       <c r="C5" t="n">
-        <v>42.64259630522314</v>
+        <v>42.04110002028908</v>
       </c>
       <c r="D5" t="n">
-        <v>2.142352189876358</v>
+        <v>2.115406190164888</v>
       </c>
       <c r="E5" t="n">
-        <v>7.165737667250683</v>
+        <v>7.024742980235754</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458313428616422</v>
+        <v>0.7457325834933182</v>
       </c>
       <c r="G5" t="n">
-        <v>32.66428612999471</v>
+        <v>32.22980809431238</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30824177163553</v>
+        <v>34.30369884069264</v>
       </c>
       <c r="I5" t="n">
-        <v>4.589437379233678</v>
+        <v>4.558222667732271</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661445892885263</v>
+        <v>4.660828646833238</v>
       </c>
       <c r="K5" t="n">
-        <v>13.72266762626214</v>
+        <v>14.36155999653551</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48202559862147</v>
+        <v>43.44566832527347</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84728953010674</v>
+        <v>99.84832834209806</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.0997521069812</v>
+        <v>84.24364622468008</v>
       </c>
       <c r="C6" t="n">
-        <v>42.17804892145364</v>
+        <v>41.35398255105143</v>
       </c>
       <c r="D6" t="n">
-        <v>2.085370194789942</v>
+        <v>2.047161842837993</v>
       </c>
       <c r="E6" t="n">
-        <v>7.613522527446861</v>
+        <v>7.432159745920378</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469503178240886</v>
+        <v>0.7468550986927609</v>
       </c>
       <c r="G6" t="n">
-        <v>31.79548584563622</v>
+        <v>31.19005401394072</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35971461990807</v>
+        <v>34.35533453986701</v>
       </c>
       <c r="I6" t="n">
-        <v>3.830269114975463</v>
+        <v>3.804236616591472</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668439486400553</v>
+        <v>4.667844366829756</v>
       </c>
       <c r="K6" t="n">
-        <v>14.9002478930188</v>
+        <v>15.7563537753199</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79421881388219</v>
+        <v>42.76304637730277</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87251562835463</v>
+        <v>99.87338270367411</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.7073345873024</v>
+        <v>82.64958612384417</v>
       </c>
       <c r="C7" t="n">
-        <v>41.38089318754267</v>
+        <v>40.35053679730474</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017956824456335</v>
+        <v>1.969440196299933</v>
       </c>
       <c r="E7" t="n">
-        <v>7.90006047425654</v>
+        <v>7.679036250878783</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479009387121087</v>
+        <v>0.7478112273138283</v>
       </c>
       <c r="G7" t="n">
-        <v>30.76763915078848</v>
+        <v>30.00590613522982</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40344318075699</v>
+        <v>34.39931645643611</v>
       </c>
       <c r="I7" t="n">
-        <v>3.19595315138125</v>
+        <v>3.174255686974274</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674380866950679</v>
+        <v>4.673820170711427</v>
       </c>
       <c r="K7" t="n">
-        <v>16.29266541269762</v>
+        <v>17.35041387615583</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22004503545484</v>
+        <v>42.19337608718966</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89360363569513</v>
+        <v>99.89432676065023</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.66618060752003</v>
+        <v>87.60000720001881</v>
       </c>
       <c r="C8" t="n">
-        <v>43.7271955275631</v>
+        <v>42.66800773518717</v>
       </c>
       <c r="D8" t="n">
-        <v>2.022269064189002</v>
+        <v>1.973698418190009</v>
       </c>
       <c r="E8" t="n">
-        <v>9.765091606945937</v>
+        <v>9.525121787202247</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494991533542295</v>
+        <v>0.7494281061323755</v>
       </c>
       <c r="G8" t="n">
-        <v>31.2837778162385</v>
+        <v>30.51201398660143</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47696105429455</v>
+        <v>34.47369288208928</v>
       </c>
       <c r="I8" t="n">
-        <v>5.684212204033889</v>
+        <v>5.682126356476123</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684369708463933</v>
+        <v>4.683925663327347</v>
       </c>
       <c r="K8" t="n">
-        <v>11.33381939247996</v>
+        <v>12.39999279998119</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74991536923923</v>
+        <v>44.74300388942248</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81093028928228</v>
+        <v>99.81100442459083</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.87275463693838</v>
+        <v>85.55861464382892</v>
       </c>
       <c r="C9" t="n">
-        <v>42.81668558737295</v>
+        <v>41.50805395811341</v>
       </c>
       <c r="D9" t="n">
-        <v>1.94159334603189</v>
+        <v>1.88126288256736</v>
       </c>
       <c r="E9" t="n">
-        <v>10.16643777582106</v>
+        <v>9.86966817811817</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508638791545282</v>
+        <v>0.7508131914858139</v>
       </c>
       <c r="G9" t="n">
-        <v>30.03575336356523</v>
+        <v>29.08302446632624</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53973844110829</v>
+        <v>34.53740680834745</v>
       </c>
       <c r="I9" t="n">
-        <v>4.745468586541568</v>
+        <v>4.743856670197542</v>
       </c>
       <c r="J9" t="n">
-        <v>4.6928992447158</v>
+        <v>4.692582446786337</v>
       </c>
       <c r="K9" t="n">
-        <v>13.12724536306161</v>
+        <v>14.44138535617109</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89817426612006</v>
+        <v>43.89272384248007</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84210521655463</v>
+        <v>99.84216315676457</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.92887851006208</v>
+        <v>83.37841489911162</v>
       </c>
       <c r="C10" t="n">
-        <v>41.60986509693829</v>
+        <v>40.06343795575218</v>
       </c>
       <c r="D10" t="n">
-        <v>1.854916652433564</v>
+        <v>1.783637724026856</v>
       </c>
       <c r="E10" t="n">
-        <v>10.37270465478334</v>
+        <v>10.01740930239013</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520311107103724</v>
+        <v>0.7520016779318074</v>
       </c>
       <c r="G10" t="n">
-        <v>28.69489597104824</v>
+        <v>27.57380696106841</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59343109267712</v>
+        <v>34.59207718486315</v>
       </c>
       <c r="I10" t="n">
-        <v>3.960704586469602</v>
+        <v>3.959471561757485</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700194441939827</v>
+        <v>4.700010487073796</v>
       </c>
       <c r="K10" t="n">
-        <v>15.07112148993792</v>
+        <v>16.62158510088837</v>
       </c>
       <c r="L10" t="n">
-        <v>43.1871948412754</v>
+        <v>43.18320314696507</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86818142815162</v>
+        <v>99.86822620360562</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.86190992570371</v>
+        <v>80.98443411013092</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15767766384905</v>
+        <v>38.28280148223615</v>
       </c>
       <c r="D11" t="n">
-        <v>1.763567640695535</v>
+        <v>1.677471199618176</v>
       </c>
       <c r="E11" t="n">
-        <v>10.41270967305096</v>
+        <v>9.971822828611851</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530309445566049</v>
+        <v>0.7530243636786489</v>
       </c>
       <c r="G11" t="n">
-        <v>27.28175949106579</v>
+        <v>25.93254584041697</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63942344960382</v>
+        <v>34.63912072921786</v>
       </c>
       <c r="I11" t="n">
-        <v>3.304975323252215</v>
+        <v>3.304046875595879</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706443403478779</v>
+        <v>4.706402272991555</v>
       </c>
       <c r="K11" t="n">
-        <v>17.13809007429629</v>
+        <v>19.01556588986907</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59421269000828</v>
+        <v>42.59164730673485</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88998042815362</v>
+        <v>99.89001467884006</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.65226279201664</v>
+        <v>78.5632805368343</v>
       </c>
       <c r="C12" t="n">
-        <v>38.46044496613352</v>
+        <v>36.37260605841731</v>
       </c>
       <c r="D12" t="n">
-        <v>1.666705161062224</v>
+        <v>1.571238187255243</v>
       </c>
       <c r="E12" t="n">
-        <v>10.30034773573247</v>
+        <v>9.799746768949975</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538890815362387</v>
+        <v>0.7539050895720076</v>
       </c>
       <c r="G12" t="n">
-        <v>25.78333163829454</v>
+        <v>24.29025686192695</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67889775066697</v>
+        <v>34.67963412031236</v>
       </c>
       <c r="I12" t="n">
-        <v>2.757284665122699</v>
+        <v>2.756592698992699</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71180675960149</v>
+        <v>4.711906809825048</v>
       </c>
       <c r="K12" t="n">
-        <v>19.34773720798337</v>
+        <v>21.43671946316572</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10001295579278</v>
+        <v>42.09889539853931</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90819512990966</v>
+        <v>99.90822092012235</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.41376406704289</v>
+        <v>76.22815943260028</v>
       </c>
       <c r="C13" t="n">
-        <v>36.648731095141</v>
+        <v>34.46288590055248</v>
       </c>
       <c r="D13" t="n">
-        <v>1.569406849452166</v>
+        <v>1.469828957067024</v>
       </c>
       <c r="E13" t="n">
-        <v>10.08236838235458</v>
+        <v>9.550506718327217</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546261683881145</v>
+        <v>0.7546631569625619</v>
       </c>
       <c r="G13" t="n">
-        <v>24.27816162100762</v>
+        <v>22.72254022327708</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71280374585326</v>
+        <v>34.71450522027786</v>
       </c>
       <c r="I13" t="n">
-        <v>2.299983747561443</v>
+        <v>2.29947042567251</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716413552425714</v>
+        <v>4.716644731016012</v>
       </c>
       <c r="K13" t="n">
-        <v>21.58623593295711</v>
+        <v>23.77184056739974</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68844173120404</v>
+        <v>41.68870151263133</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92340875930215</v>
+        <v>99.92342798058354</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.68994889405933</v>
+        <v>83.23201428334464</v>
       </c>
       <c r="C14" t="n">
-        <v>40.49441397372884</v>
+        <v>38.80488321954299</v>
       </c>
       <c r="D14" t="n">
-        <v>1.571269585649777</v>
+        <v>1.471592246158246</v>
       </c>
       <c r="E14" t="n">
-        <v>12.25281885602311</v>
+        <v>11.96784424652468</v>
       </c>
       <c r="F14" t="n">
-        <v>0.755521837653233</v>
+        <v>0.7555684931282572</v>
       </c>
       <c r="G14" t="n">
-        <v>25.96286670033151</v>
+        <v>24.65643074376242</v>
       </c>
       <c r="H14" t="n">
-        <v>36.40989374983952</v>
+        <v>36.66278197322912</v>
       </c>
       <c r="I14" t="n">
-        <v>3.015566679229473</v>
+        <v>2.9954934984903</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722011485332706</v>
+        <v>4.722303082051607</v>
       </c>
       <c r="K14" t="n">
-        <v>15.31005110594069</v>
+        <v>16.76798571665537</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09513519591684</v>
+        <v>44.32740092237873</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89960027558637</v>
+        <v>99.90026985857709</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.04969231125772</v>
+        <v>82.52033555505908</v>
       </c>
       <c r="C15" t="n">
-        <v>40.2968359314255</v>
+        <v>38.55579776496726</v>
       </c>
       <c r="D15" t="n">
-        <v>1.544655273402058</v>
+        <v>1.445558659162723</v>
       </c>
       <c r="E15" t="n">
-        <v>12.4887633180192</v>
+        <v>12.17258466762901</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562755582304435</v>
+        <v>0.7563311283699218</v>
       </c>
       <c r="G15" t="n">
-        <v>25.5473425449077</v>
+        <v>24.22023971568207</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47045416408051</v>
+        <v>36.69978765814656</v>
       </c>
       <c r="I15" t="n">
-        <v>2.515479213677537</v>
+        <v>2.49876417375677</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726722238940271</v>
+        <v>4.727069552312011</v>
       </c>
       <c r="K15" t="n">
-        <v>15.95030768874229</v>
+        <v>17.47966444494093</v>
       </c>
       <c r="L15" t="n">
-        <v>43.66909063874252</v>
+        <v>43.88132963735598</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91623425891031</v>
+        <v>99.91679184726416</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.65590670146976</v>
+        <v>80.14479081761603</v>
       </c>
       <c r="C16" t="n">
-        <v>38.29262319778222</v>
+        <v>36.56622001308912</v>
       </c>
       <c r="D16" t="n">
-        <v>1.452479731020557</v>
+        <v>1.355978893950759</v>
       </c>
       <c r="E16" t="n">
-        <v>12.09318193846996</v>
+        <v>11.76561367451822</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569232710371998</v>
+        <v>0.7569867235209835</v>
       </c>
       <c r="G16" t="n">
-        <v>24.02283400502074</v>
+        <v>22.71933667494005</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50168931372038</v>
+        <v>36.73159938971648</v>
       </c>
       <c r="I16" t="n">
-        <v>2.098027998218422</v>
+        <v>2.084108438963397</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730770443982498</v>
+        <v>4.731167022006146</v>
       </c>
       <c r="K16" t="n">
-        <v>18.34409329853024</v>
+        <v>19.85520918238398</v>
       </c>
       <c r="L16" t="n">
-        <v>43.2934090810854</v>
+        <v>43.50916068858921</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93012557739786</v>
+        <v>99.93058988406231</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>83.28227976580207</v>
+        <v>81.9292350798091</v>
       </c>
       <c r="C17" t="n">
-        <v>39.48412364242625</v>
+        <v>37.86619784113743</v>
       </c>
       <c r="D17" t="n">
-        <v>1.453696283033319</v>
+        <v>1.357121633396522</v>
       </c>
       <c r="E17" t="n">
-        <v>12.85753505080648</v>
+        <v>12.58281727693119</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757557246513222</v>
+        <v>0.7576246675131395</v>
       </c>
       <c r="G17" t="n">
-        <v>24.44840574048852</v>
+        <v>23.20054567292631</v>
       </c>
       <c r="H17" t="n">
-        <v>36.93771295169565</v>
+        <v>37.22461710050793</v>
       </c>
       <c r="I17" t="n">
-        <v>2.092639702557229</v>
+        <v>2.071354556576873</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734732790707637</v>
+        <v>4.735154171957122</v>
       </c>
       <c r="K17" t="n">
-        <v>16.71772023419794</v>
+        <v>18.07076492019089</v>
       </c>
       <c r="L17" t="n">
-        <v>43.72845984206935</v>
+        <v>43.99405022499289</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93030371869354</v>
+        <v>99.93101298632122</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.94466975965111</v>
+        <v>79.58950449861699</v>
       </c>
       <c r="C18" t="n">
-        <v>37.47022871782355</v>
+        <v>35.84606680243294</v>
       </c>
       <c r="D18" t="n">
-        <v>1.367004937773218</v>
+        <v>1.27254731581154</v>
       </c>
       <c r="E18" t="n">
-        <v>12.38162774115604</v>
+        <v>12.08656629760995</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758101662855815</v>
+        <v>0.7581727732235255</v>
       </c>
       <c r="G18" t="n">
-        <v>22.99042224844491</v>
+        <v>21.7547133542887</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96425813317398</v>
+        <v>37.25154735512424</v>
       </c>
       <c r="I18" t="n">
-        <v>1.74511964339829</v>
+        <v>1.727377569911992</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738135392848844</v>
+        <v>4.738579832647035</v>
       </c>
       <c r="K18" t="n">
-        <v>19.05533024034889</v>
+        <v>20.41049550138302</v>
       </c>
       <c r="L18" t="n">
-        <v>43.41631216120098</v>
+        <v>43.68590006961245</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94187111937342</v>
+        <v>99.94246237342841</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.97770717583026</v>
+        <v>78.68381278901816</v>
       </c>
       <c r="C19" t="n">
-        <v>36.7725717346589</v>
+        <v>35.20622158271157</v>
       </c>
       <c r="D19" t="n">
-        <v>1.331832956970335</v>
+        <v>1.240480941074709</v>
       </c>
       <c r="E19" t="n">
-        <v>12.30558275200165</v>
+        <v>12.02206203451599</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585614369711865</v>
+        <v>0.7586354018303553</v>
       </c>
       <c r="G19" t="n">
-        <v>22.39889644804095</v>
+        <v>21.20652565074065</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98667624662266</v>
+        <v>37.27427783564767</v>
       </c>
       <c r="I19" t="n">
-        <v>1.455148354153551</v>
+        <v>1.440359663769077</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741008981069916</v>
+        <v>4.74147126143972</v>
       </c>
       <c r="K19" t="n">
-        <v>20.02229282416975</v>
+        <v>21.31618721098183</v>
       </c>
       <c r="L19" t="n">
-        <v>43.1566598955214</v>
+        <v>43.42960849603126</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95152445435005</v>
+        <v>99.95201728972467</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.48660091612032</v>
+        <v>76.22529073561216</v>
       </c>
       <c r="C20" t="n">
-        <v>34.50587127235107</v>
+        <v>32.96923192805697</v>
       </c>
       <c r="D20" t="n">
-        <v>1.240413509265161</v>
+        <v>1.15260806565339</v>
       </c>
       <c r="E20" t="n">
-        <v>11.66311448738416</v>
+        <v>11.3706012551388</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589573461133307</v>
+        <v>0.7590338120618982</v>
       </c>
       <c r="G20" t="n">
-        <v>20.86139526835592</v>
+        <v>19.70430314580471</v>
       </c>
       <c r="H20" t="n">
-        <v>37.0059803695979</v>
+        <v>37.29385305402961</v>
       </c>
       <c r="I20" t="n">
-        <v>1.213256522195523</v>
+        <v>1.200930077536897</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743483413208317</v>
+        <v>4.743961325386864</v>
       </c>
       <c r="K20" t="n">
-        <v>22.51339908387969</v>
+        <v>23.77470926438782</v>
       </c>
       <c r="L20" t="n">
-        <v>42.94030885615388</v>
+        <v>43.21604881689495</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95957921238464</v>
+        <v>99.95999000933975</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>83.18018782203744</v>
+        <v>82.06313564919134</v>
       </c>
       <c r="C21" t="n">
-        <v>37.969097960718</v>
+        <v>36.58703307996471</v>
       </c>
       <c r="D21" t="n">
-        <v>1.241324102374731</v>
+        <v>1.153415893345363</v>
       </c>
       <c r="E21" t="n">
-        <v>13.54820705201683</v>
+        <v>13.32386454343981</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595145000984059</v>
+        <v>0.7595657956136358</v>
       </c>
       <c r="G21" t="n">
-        <v>22.4479255910007</v>
+        <v>21.37582957849055</v>
       </c>
       <c r="H21" t="n">
-        <v>38.60436250443293</v>
+        <v>38.97770746352617</v>
       </c>
       <c r="I21" t="n">
-        <v>1.831888446498804</v>
+        <v>1.725466152190582</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746965625615037</v>
+        <v>4.747286222585224</v>
       </c>
       <c r="K21" t="n">
-        <v>16.81981217796256</v>
+        <v>17.93686435080867</v>
       </c>
       <c r="L21" t="n">
-        <v>45.15007170680316</v>
+        <v>45.41862731346671</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93898184548372</v>
+        <v>99.94252474424007</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>44.87760629397405</v>
+        <v>45.10217066061684</v>
       </c>
       <c r="M2" t="n">
-        <v>99.94172155283161</v>
+        <v>99.98510050599754</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.94722243086923</v>
+        <v>88.05854280305377</v>
       </c>
       <c r="C3" t="n">
-        <v>45.87101057721738</v>
+        <v>45.93414561306977</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228568780701174</v>
+        <v>2.228806570806017</v>
       </c>
       <c r="E3" t="n">
-        <v>5.669108698762296</v>
+        <v>5.711207134475406</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428562602337246</v>
+        <v>0.7429355236020059</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95392547346946</v>
+        <v>33.97468642393753</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17138797075133</v>
+        <v>34.17503408569226</v>
       </c>
       <c r="I3" t="n">
-        <v>6.538523620490451</v>
+        <v>6.582526042027997</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642851626460779</v>
+        <v>4.643347022512536</v>
       </c>
       <c r="K3" t="n">
-        <v>12.05277756913079</v>
+        <v>11.94145719694624</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84149534224372</v>
+        <v>48.88812631288772</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7652834885919</v>
+        <v>106.7637291229037</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.91574534563298</v>
+        <v>87.23773545121169</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4711104085541</v>
+        <v>42.75106802903836</v>
       </c>
       <c r="D4" t="n">
-        <v>2.178195062200131</v>
+        <v>2.189749945820933</v>
       </c>
       <c r="E4" t="n">
-        <v>6.450996275960444</v>
+        <v>6.527286430051105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444118390088862</v>
+        <v>0.7444959671119004</v>
       </c>
       <c r="G4" t="n">
-        <v>33.18644389577824</v>
+        <v>33.37932897837612</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24294459440877</v>
+        <v>34.2468144871474</v>
       </c>
       <c r="I4" t="n">
-        <v>5.460179684470994</v>
+        <v>5.496959848254849</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652573993805539</v>
+        <v>4.653099794449377</v>
       </c>
       <c r="K4" t="n">
-        <v>13.08425465436702</v>
+        <v>12.76226454878829</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26300928095415</v>
+        <v>44.30381947656146</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81837434387526</v>
+        <v>99.81715205438812</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.63844000346448</v>
+        <v>86.03482638614679</v>
       </c>
       <c r="C5" t="n">
-        <v>42.04110002028908</v>
+        <v>42.40141890188606</v>
       </c>
       <c r="D5" t="n">
-        <v>2.115406190164888</v>
+        <v>2.130959554214797</v>
       </c>
       <c r="E5" t="n">
-        <v>7.024742980235754</v>
+        <v>7.116865932427194</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457325834933182</v>
+        <v>0.7458196367005203</v>
       </c>
       <c r="G5" t="n">
-        <v>32.22980809431238</v>
+        <v>32.48316098169052</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30369884069264</v>
+        <v>34.30770328822393</v>
       </c>
       <c r="I5" t="n">
-        <v>4.558222667732271</v>
+        <v>4.588944263511564</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660828646833238</v>
+        <v>4.661372729378251</v>
       </c>
       <c r="K5" t="n">
-        <v>14.36155999653551</v>
+        <v>13.96517361385324</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44566832527347</v>
+        <v>43.48071415514249</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84832834209806</v>
+        <v>99.84730667088178</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.24364622468008</v>
+        <v>84.7254044310266</v>
       </c>
       <c r="C6" t="n">
-        <v>41.35398255105143</v>
+        <v>41.80473751984505</v>
       </c>
       <c r="D6" t="n">
-        <v>2.047161842837993</v>
+        <v>2.0672051078828</v>
       </c>
       <c r="E6" t="n">
-        <v>7.432159745920378</v>
+        <v>7.542255929687214</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468550986927609</v>
+        <v>0.7469434245702756</v>
       </c>
       <c r="G6" t="n">
-        <v>31.19005401394072</v>
+        <v>31.51132369862022</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35533453986701</v>
+        <v>34.35939753023267</v>
       </c>
       <c r="I6" t="n">
-        <v>3.804236616591472</v>
+        <v>3.829882336469212</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667844366829756</v>
+        <v>4.668396403564222</v>
       </c>
       <c r="K6" t="n">
-        <v>15.7563537753199</v>
+        <v>15.27459556897338</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76304637730277</v>
+        <v>42.79319623719515</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87338270367411</v>
+        <v>99.87252932601358</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.64958612384417</v>
+        <v>83.17967005683879</v>
       </c>
       <c r="C7" t="n">
-        <v>40.35053679730474</v>
+        <v>40.85392188886007</v>
       </c>
       <c r="D7" t="n">
-        <v>1.969440196299933</v>
+        <v>1.992046462197438</v>
       </c>
       <c r="E7" t="n">
-        <v>7.679036250878783</v>
+        <v>7.800646800805061</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478112273138283</v>
+        <v>0.7478999780544513</v>
       </c>
       <c r="G7" t="n">
-        <v>30.00590613522982</v>
+        <v>30.36564715016829</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39931645643611</v>
+        <v>34.40339899050475</v>
       </c>
       <c r="I7" t="n">
-        <v>3.174255686974274</v>
+        <v>3.195655812268464</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673820170711427</v>
+        <v>4.674374862840319</v>
       </c>
       <c r="K7" t="n">
-        <v>17.35041387615583</v>
+        <v>16.82032994316122</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19337608718966</v>
+        <v>42.21936254752124</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89432676065023</v>
+        <v>99.89361437954253</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.60000720001881</v>
+        <v>87.95368856222562</v>
       </c>
       <c r="C8" t="n">
-        <v>42.66800773518717</v>
+        <v>43.13024489638335</v>
       </c>
       <c r="D8" t="n">
-        <v>1.973698418190009</v>
+        <v>1.996253152384297</v>
       </c>
       <c r="E8" t="n">
-        <v>9.525121787202247</v>
+        <v>9.612479760872608</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494281061323755</v>
+        <v>0.7494793506033041</v>
       </c>
       <c r="G8" t="n">
-        <v>30.51201398660143</v>
+        <v>30.86311262558831</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47369288208928</v>
+        <v>34.47605012775198</v>
       </c>
       <c r="I8" t="n">
-        <v>5.682126356476123</v>
+        <v>5.572067603754475</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683925663327347</v>
+        <v>4.684245941270649</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39999279998119</v>
+        <v>12.04631143777437</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74300388942248</v>
+        <v>44.63809947834238</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81100442459083</v>
+        <v>99.81465581250009</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.55861464382892</v>
+        <v>85.9716154340845</v>
       </c>
       <c r="C9" t="n">
-        <v>41.50805395811341</v>
+        <v>42.01315003960661</v>
       </c>
       <c r="D9" t="n">
-        <v>1.88126288256736</v>
+        <v>1.906524575476298</v>
       </c>
       <c r="E9" t="n">
-        <v>9.86966817811817</v>
+        <v>9.955707337376341</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508131914858139</v>
+        <v>0.7508311151464535</v>
       </c>
       <c r="G9" t="n">
-        <v>29.08302446632624</v>
+        <v>29.47586213005988</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53740680834745</v>
+        <v>34.53823129673686</v>
       </c>
       <c r="I9" t="n">
-        <v>4.743856670197542</v>
+        <v>4.651764509623342</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692582446786337</v>
+        <v>4.692694469665333</v>
       </c>
       <c r="K9" t="n">
-        <v>14.44138535617109</v>
+        <v>14.0283845659155</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89272384248007</v>
+        <v>43.80368573881803</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84216315676457</v>
+        <v>99.84522034434013</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.37841489911162</v>
+        <v>83.75176903723214</v>
       </c>
       <c r="C10" t="n">
-        <v>40.06343795575218</v>
+        <v>40.51515716532098</v>
       </c>
       <c r="D10" t="n">
-        <v>1.783637724026856</v>
+        <v>1.806932442374661</v>
       </c>
       <c r="E10" t="n">
-        <v>10.01740930239013</v>
+        <v>10.08272252583009</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520016779318074</v>
+        <v>0.751991318343229</v>
       </c>
       <c r="G10" t="n">
-        <v>27.57380696106841</v>
+        <v>27.93611592258755</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59207718486315</v>
+        <v>34.59160064378853</v>
       </c>
       <c r="I10" t="n">
-        <v>3.959471561757485</v>
+        <v>3.882460444662913</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700010487073796</v>
+        <v>4.699945739645179</v>
       </c>
       <c r="K10" t="n">
-        <v>16.62158510088837</v>
+        <v>16.24823096276785</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18320314696507</v>
+        <v>43.10739619108831</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86822620360562</v>
+        <v>99.87078431917715</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.98443411013092</v>
+        <v>81.44513872855777</v>
       </c>
       <c r="C11" t="n">
-        <v>38.28280148223615</v>
+        <v>38.81036251777544</v>
       </c>
       <c r="D11" t="n">
-        <v>1.677471199618176</v>
+        <v>1.704535541833523</v>
       </c>
       <c r="E11" t="n">
-        <v>9.971822828611851</v>
+        <v>10.05129117240398</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530243636786489</v>
+        <v>0.7529883929441108</v>
       </c>
       <c r="G11" t="n">
-        <v>25.93254584041697</v>
+        <v>26.35300655084394</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63912072921786</v>
+        <v>34.6374660754291</v>
       </c>
       <c r="I11" t="n">
-        <v>3.304046875595879</v>
+        <v>3.239673539202422</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706402272991555</v>
+        <v>4.706177455900691</v>
       </c>
       <c r="K11" t="n">
-        <v>19.01556588986907</v>
+        <v>18.55486127144223</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59164730673485</v>
+        <v>42.52693008731947</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89001467884006</v>
+        <v>99.89215387653715</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.5632805368343</v>
+        <v>78.99258725852603</v>
       </c>
       <c r="C12" t="n">
-        <v>36.37260605841731</v>
+        <v>36.85922484621636</v>
       </c>
       <c r="D12" t="n">
-        <v>1.571238187255243</v>
+        <v>1.596656548150681</v>
       </c>
       <c r="E12" t="n">
-        <v>9.799746768949975</v>
+        <v>9.865619055066214</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539050895720076</v>
+        <v>0.753847200260385</v>
       </c>
       <c r="G12" t="n">
-        <v>24.29025686192695</v>
+        <v>24.68514116613959</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67963412031236</v>
+        <v>34.67697121197771</v>
       </c>
       <c r="I12" t="n">
-        <v>2.756592698992699</v>
+        <v>2.702807075304045</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711906809825048</v>
+        <v>4.711545001627404</v>
       </c>
       <c r="K12" t="n">
-        <v>21.43671946316572</v>
+        <v>21.00741274147397</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09889539853931</v>
+        <v>42.04337148066514</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90822092012235</v>
+        <v>99.91000906835548</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.22815943260028</v>
+        <v>76.66616649785108</v>
       </c>
       <c r="C13" t="n">
-        <v>34.46288590055248</v>
+        <v>34.95023308051191</v>
       </c>
       <c r="D13" t="n">
-        <v>1.469828957067024</v>
+        <v>1.495361308425998</v>
       </c>
       <c r="E13" t="n">
-        <v>9.550506718327217</v>
+        <v>9.61548133859467</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546631569625619</v>
+        <v>0.7545861546456651</v>
       </c>
       <c r="G13" t="n">
-        <v>22.72254022327708</v>
+        <v>23.11906404394451</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71450522027786</v>
+        <v>34.71096311370059</v>
       </c>
       <c r="I13" t="n">
-        <v>2.29947042567251</v>
+        <v>2.254547072004242</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716644731016012</v>
+        <v>4.716163466535405</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77184056739974</v>
+        <v>23.33383350214894</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68870151263133</v>
+        <v>41.64085544302515</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92342798058354</v>
+        <v>99.92492202568599</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.23201428334464</v>
+        <v>83.59451480566072</v>
       </c>
       <c r="C14" t="n">
-        <v>38.80488321954299</v>
+        <v>39.27327244963017</v>
       </c>
       <c r="D14" t="n">
-        <v>1.471592246158246</v>
+        <v>1.497089191894754</v>
       </c>
       <c r="E14" t="n">
-        <v>11.96784424652468</v>
+        <v>12.01494236340373</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555684931282572</v>
+        <v>0.7554580756556698</v>
       </c>
       <c r="G14" t="n">
-        <v>24.65643074376242</v>
+        <v>25.05116291367199</v>
       </c>
       <c r="H14" t="n">
-        <v>36.66278197322912</v>
+        <v>36.6564563722365</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9954934984903</v>
+        <v>2.897792915950147</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722303082051607</v>
+        <v>4.721612972847934</v>
       </c>
       <c r="K14" t="n">
-        <v>16.76798571665537</v>
+        <v>16.40548519433928</v>
       </c>
       <c r="L14" t="n">
-        <v>44.32740092237873</v>
+        <v>44.22476074291531</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90026985857709</v>
+        <v>99.90351838688476</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.52033555505908</v>
+        <v>82.93149149359762</v>
       </c>
       <c r="C15" t="n">
-        <v>38.55579776496726</v>
+        <v>39.05810047088947</v>
       </c>
       <c r="D15" t="n">
-        <v>1.445558659162723</v>
+        <v>1.472778988486238</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17258466762901</v>
+        <v>12.22270222545668</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563311283699218</v>
+        <v>0.7561920442434231</v>
       </c>
       <c r="G15" t="n">
-        <v>24.22023971568207</v>
+        <v>24.64437428053753</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69978765814656</v>
+        <v>36.69207011227392</v>
       </c>
       <c r="I15" t="n">
-        <v>2.49876417375677</v>
+        <v>2.417173566078447</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727069552312011</v>
+        <v>4.726200276521393</v>
       </c>
       <c r="K15" t="n">
-        <v>17.47966444494093</v>
+        <v>17.06850850640237</v>
       </c>
       <c r="L15" t="n">
-        <v>43.88132963735598</v>
+        <v>43.79289677504289</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91679184726416</v>
+        <v>99.91950575233473</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.14479081761603</v>
+        <v>80.65393499451545</v>
       </c>
       <c r="C16" t="n">
-        <v>36.56622001308912</v>
+        <v>37.15420959048592</v>
       </c>
       <c r="D16" t="n">
-        <v>1.355978893950759</v>
+        <v>1.386443623906691</v>
       </c>
       <c r="E16" t="n">
-        <v>11.76561367451822</v>
+        <v>11.84219688822735</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569867235209835</v>
+        <v>0.7568220921537751</v>
       </c>
       <c r="G16" t="n">
-        <v>22.71933667494005</v>
+        <v>23.19970331837782</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73159938971648</v>
+        <v>36.72264139674684</v>
       </c>
       <c r="I16" t="n">
-        <v>2.084108438963397</v>
+        <v>2.015989599141878</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731167022006146</v>
+        <v>4.730138075961092</v>
       </c>
       <c r="K16" t="n">
-        <v>19.85520918238398</v>
+        <v>19.34606500548454</v>
       </c>
       <c r="L16" t="n">
-        <v>43.50916068858921</v>
+        <v>43.43258169386068</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93058988406231</v>
+        <v>99.93285628983114</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.9292350798091</v>
+        <v>82.46192156665639</v>
       </c>
       <c r="C17" t="n">
-        <v>37.86619784113743</v>
+        <v>38.46223617318132</v>
       </c>
       <c r="D17" t="n">
-        <v>1.357121633396522</v>
+        <v>1.387570352882457</v>
       </c>
       <c r="E17" t="n">
-        <v>12.58281727693119</v>
+        <v>12.65841179015761</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576246675131395</v>
+        <v>0.757437143040826</v>
       </c>
       <c r="G17" t="n">
-        <v>23.20054567292631</v>
+        <v>23.69007420995283</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22461710050793</v>
+        <v>37.22400205083918</v>
       </c>
       <c r="I17" t="n">
-        <v>2.071354556576873</v>
+        <v>2.010443875778332</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735154171957122</v>
+        <v>4.73398214400516</v>
       </c>
       <c r="K17" t="n">
-        <v>18.07076492019089</v>
+        <v>17.53807843334362</v>
       </c>
       <c r="L17" t="n">
-        <v>43.99405022499289</v>
+        <v>43.93272501468525</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93101298632122</v>
+        <v>99.93303962121018</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.58950449861699</v>
+        <v>80.25566940333364</v>
       </c>
       <c r="C18" t="n">
-        <v>35.84606680243294</v>
+        <v>36.56646964879132</v>
       </c>
       <c r="D18" t="n">
-        <v>1.27254731581154</v>
+        <v>1.307355270254854</v>
       </c>
       <c r="E18" t="n">
-        <v>12.08656629760995</v>
+        <v>12.2060550354861</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581727732235255</v>
+        <v>0.7579645703795025</v>
       </c>
       <c r="G18" t="n">
-        <v>21.7547133542887</v>
+        <v>22.32055715717215</v>
       </c>
       <c r="H18" t="n">
-        <v>37.25154735512424</v>
+        <v>37.24992229586142</v>
       </c>
       <c r="I18" t="n">
-        <v>1.727377569911992</v>
+        <v>1.676536509307732</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738579832647035</v>
+        <v>4.737278564871889</v>
       </c>
       <c r="K18" t="n">
-        <v>20.41049550138302</v>
+        <v>19.74433059666634</v>
       </c>
       <c r="L18" t="n">
-        <v>43.68590006961245</v>
+        <v>43.63335409132628</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94246237342841</v>
+        <v>99.94415433678395</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.68381278901816</v>
+        <v>79.44581590462342</v>
       </c>
       <c r="C19" t="n">
-        <v>35.20622158271157</v>
+        <v>36.01493082754178</v>
       </c>
       <c r="D19" t="n">
-        <v>1.240480941074709</v>
+        <v>1.278558308257301</v>
       </c>
       <c r="E19" t="n">
-        <v>12.02206203451599</v>
+        <v>12.17018255444862</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7586354018303553</v>
+        <v>0.7584091433403749</v>
       </c>
       <c r="G19" t="n">
-        <v>21.20652565074065</v>
+        <v>21.82890484900193</v>
       </c>
       <c r="H19" t="n">
-        <v>37.27427783564767</v>
+        <v>37.27177068943349</v>
       </c>
       <c r="I19" t="n">
-        <v>1.440359663769077</v>
+        <v>1.397933214264351</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74147126143972</v>
+        <v>4.740057145877342</v>
       </c>
       <c r="K19" t="n">
-        <v>21.31618721098183</v>
+        <v>20.55418409537658</v>
       </c>
       <c r="L19" t="n">
-        <v>43.42960849603126</v>
+        <v>43.38431461848975</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95201728972467</v>
+        <v>99.95342954140811</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.22529073561216</v>
+        <v>77.00443516613358</v>
       </c>
       <c r="C20" t="n">
-        <v>32.96923192805697</v>
+        <v>33.78883150742843</v>
       </c>
       <c r="D20" t="n">
-        <v>1.15260806565339</v>
+        <v>1.190676426426951</v>
       </c>
       <c r="E20" t="n">
-        <v>11.3706012551388</v>
+        <v>11.52791872555964</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7590338120618982</v>
+        <v>0.7587917837236816</v>
       </c>
       <c r="G20" t="n">
-        <v>19.70430314580471</v>
+        <v>20.32849206060067</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29385305402961</v>
+        <v>37.29057542662364</v>
       </c>
       <c r="I20" t="n">
-        <v>1.200930077536897</v>
+        <v>1.165532094925977</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743961325386864</v>
+        <v>4.742448648273009</v>
       </c>
       <c r="K20" t="n">
-        <v>23.77470926438782</v>
+        <v>22.99556483386642</v>
       </c>
       <c r="L20" t="n">
-        <v>43.21604881689495</v>
+        <v>43.17677218053112</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95999000933975</v>
+        <v>99.96116852182598</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.06313564919134</v>
+        <v>82.69585240962429</v>
       </c>
       <c r="C21" t="n">
-        <v>36.58703307996471</v>
+        <v>37.33512171812112</v>
       </c>
       <c r="D21" t="n">
-        <v>1.153415893345363</v>
+        <v>1.191466624487922</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32386454343981</v>
+        <v>13.43856548102523</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7595657956136358</v>
+        <v>0.7592953594919354</v>
       </c>
       <c r="G21" t="n">
-        <v>21.37582957849055</v>
+        <v>21.97057188382492</v>
       </c>
       <c r="H21" t="n">
-        <v>38.97770746352617</v>
+        <v>38.94391221697042</v>
       </c>
       <c r="I21" t="n">
-        <v>1.725466152190582</v>
+        <v>1.646444846999275</v>
       </c>
       <c r="J21" t="n">
-        <v>4.747286222585224</v>
+        <v>4.745595996824595</v>
       </c>
       <c r="K21" t="n">
-        <v>17.93686435080867</v>
+        <v>17.30414759037568</v>
       </c>
       <c r="L21" t="n">
-        <v>45.41862731346671</v>
+        <v>45.30588559481191</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94252474424007</v>
+        <v>99.94515490330872</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_65_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.10217066061684</v>
+        <v>44.19702418701657</v>
       </c>
       <c r="M2" t="n">
-        <v>99.98510050599754</v>
+        <v>93.67963839787328</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.05854280305377</v>
+        <v>81.394845855659</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93414561306977</v>
+        <v>43.15040141121455</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228806570806017</v>
+        <v>2.176011806100378</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711207134475406</v>
+        <v>4.13889121271627</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429355236020059</v>
+        <v>0.7375750116705223</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97468642393753</v>
+        <v>32.73084425009319</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17503408569226</v>
+        <v>33.92845053684402</v>
       </c>
       <c r="I3" t="n">
-        <v>6.582526042027997</v>
+        <v>3.073229215293843</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643347022512536</v>
+        <v>4.609843822940764</v>
       </c>
       <c r="K3" t="n">
-        <v>11.94145719694624</v>
+        <v>18.60515414434101</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88812631288772</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7637291229037</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.23773545121169</v>
+        <v>88.40601411888861</v>
       </c>
       <c r="C4" t="n">
-        <v>42.75106802903836</v>
+        <v>42.72789605616445</v>
       </c>
       <c r="D4" t="n">
-        <v>2.189749945820933</v>
+        <v>2.181695597615309</v>
       </c>
       <c r="E4" t="n">
-        <v>6.527286430051105</v>
+        <v>6.502742945457593</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444959671119004</v>
+        <v>0.7395015741005631</v>
       </c>
       <c r="G4" t="n">
-        <v>33.37932897837612</v>
+        <v>33.41556215931298</v>
       </c>
       <c r="H4" t="n">
-        <v>34.2468144871474</v>
+        <v>34.01707240862589</v>
       </c>
       <c r="I4" t="n">
-        <v>5.496959848254849</v>
+        <v>6.927554595647753</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653099794449377</v>
+        <v>4.621884838128519</v>
       </c>
       <c r="K4" t="n">
-        <v>12.76226454878829</v>
+        <v>11.5939858811114</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30381947656146</v>
+        <v>45.44780116908095</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81715205438812</v>
+        <v>99.76968310635679</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.03482638614679</v>
+        <v>87.220740127477</v>
       </c>
       <c r="C5" t="n">
-        <v>42.40141890188606</v>
+        <v>42.61638864558148</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130959554214797</v>
+        <v>2.124960855258991</v>
       </c>
       <c r="E5" t="n">
-        <v>7.116865932427194</v>
+        <v>7.297927700327719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458196367005203</v>
+        <v>0.7411367181520343</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48316098169052</v>
+        <v>32.5465943198617</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30770328822393</v>
+        <v>34.09228903499357</v>
       </c>
       <c r="I5" t="n">
-        <v>4.588944263511564</v>
+        <v>5.785727010432776</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661372729378251</v>
+        <v>4.632104488450214</v>
       </c>
       <c r="K5" t="n">
-        <v>13.96517361385324</v>
+        <v>12.77925987252299</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48071415514249</v>
+        <v>44.41191940979421</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84730667088178</v>
+        <v>99.80756792789867</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.7254044310266</v>
+        <v>85.69173754250912</v>
       </c>
       <c r="C6" t="n">
-        <v>41.80473751984505</v>
+        <v>41.985190204526</v>
       </c>
       <c r="D6" t="n">
-        <v>2.0672051078828</v>
+        <v>2.051393163569019</v>
       </c>
       <c r="E6" t="n">
-        <v>7.542255929687214</v>
+        <v>7.850351258044788</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469434245702756</v>
+        <v>0.7425293300511635</v>
       </c>
       <c r="G6" t="n">
-        <v>31.51132369862022</v>
+        <v>31.41980753197503</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35939753023267</v>
+        <v>34.15634918235352</v>
       </c>
       <c r="I6" t="n">
-        <v>3.829882336469212</v>
+        <v>4.830498763695815</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668396403564222</v>
+        <v>4.640808312819773</v>
       </c>
       <c r="K6" t="n">
-        <v>15.27459556897338</v>
+        <v>14.30826245749088</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79319623719515</v>
+        <v>43.54583269880443</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87252932601358</v>
+        <v>99.83928536082132</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.17967005683879</v>
+        <v>84.03476886053603</v>
       </c>
       <c r="C7" t="n">
-        <v>40.85392188886007</v>
+        <v>41.07801520773576</v>
       </c>
       <c r="D7" t="n">
-        <v>1.992046462197438</v>
+        <v>1.972282761853029</v>
       </c>
       <c r="E7" t="n">
-        <v>7.800646800805061</v>
+        <v>8.219584058582615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478999780544513</v>
+        <v>0.7437168422545327</v>
       </c>
       <c r="G7" t="n">
-        <v>30.36564715016829</v>
+        <v>30.20812678747595</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40339899050475</v>
+        <v>34.2109747437085</v>
       </c>
       <c r="I7" t="n">
-        <v>3.195655812268464</v>
+        <v>4.031853402570571</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674374862840319</v>
+        <v>4.64823026409083</v>
       </c>
       <c r="K7" t="n">
-        <v>16.82032994316122</v>
+        <v>15.96523113946398</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21936254752124</v>
+        <v>42.82257313158647</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89361437954253</v>
+        <v>99.86581947878621</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.95368856222562</v>
+        <v>82.11141567037913</v>
       </c>
       <c r="C8" t="n">
-        <v>43.13024489638335</v>
+        <v>39.78033689925515</v>
       </c>
       <c r="D8" t="n">
-        <v>1.996253152384297</v>
+        <v>1.880952324293022</v>
       </c>
       <c r="E8" t="n">
-        <v>9.612479760872608</v>
+        <v>8.399704497944578</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494793506033041</v>
+        <v>0.7447326208791486</v>
       </c>
       <c r="G8" t="n">
-        <v>30.86311262558831</v>
+        <v>28.80927998379743</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47605012775198</v>
+        <v>34.25770056044082</v>
       </c>
       <c r="I8" t="n">
-        <v>5.572067603754475</v>
+        <v>3.364466802529456</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684245941270649</v>
+        <v>4.654578880494679</v>
       </c>
       <c r="K8" t="n">
-        <v>12.04631143777437</v>
+        <v>17.88858432962087</v>
       </c>
       <c r="L8" t="n">
-        <v>44.63809947834238</v>
+        <v>42.2190828432748</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81465581250009</v>
+        <v>99.88800407215081</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.9716154340845</v>
+        <v>80.0146803526541</v>
       </c>
       <c r="C9" t="n">
-        <v>42.01315003960661</v>
+        <v>38.20522116509602</v>
       </c>
       <c r="D9" t="n">
-        <v>1.906524575476298</v>
+        <v>1.782141941938113</v>
       </c>
       <c r="E9" t="n">
-        <v>9.955707337376341</v>
+        <v>8.426283838066889</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508311151464535</v>
+        <v>0.7456034882183615</v>
       </c>
       <c r="G9" t="n">
-        <v>29.47586213005988</v>
+        <v>27.29586790322352</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53823129673686</v>
+        <v>34.29776045804461</v>
       </c>
       <c r="I9" t="n">
-        <v>4.651764509623342</v>
+        <v>2.807000921797851</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692694469665333</v>
+        <v>4.66002180136476</v>
       </c>
       <c r="K9" t="n">
-        <v>14.0283845659155</v>
+        <v>19.98531964734589</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80368573881803</v>
+        <v>41.71600177637671</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84522034434013</v>
+        <v>99.90654258881862</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.75176903723214</v>
+        <v>85.1767484932101</v>
       </c>
       <c r="C10" t="n">
-        <v>40.51515716532098</v>
+        <v>41.64783891923827</v>
       </c>
       <c r="D10" t="n">
-        <v>1.806932442374661</v>
+        <v>1.784252992366105</v>
       </c>
       <c r="E10" t="n">
-        <v>10.08272252583009</v>
+        <v>10.38949065221821</v>
       </c>
       <c r="F10" t="n">
-        <v>0.751991318343229</v>
+        <v>0.7464866987673504</v>
       </c>
       <c r="G10" t="n">
-        <v>27.93611592258755</v>
+        <v>28.7769428551078</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59160064378853</v>
+        <v>35.78712955750871</v>
       </c>
       <c r="I10" t="n">
-        <v>3.882460444662913</v>
+        <v>3.026903869945977</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699945739645179</v>
+        <v>4.66554186729594</v>
       </c>
       <c r="K10" t="n">
-        <v>16.24823096276785</v>
+        <v>14.82325150678991</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10739619108831</v>
+        <v>43.42813215500107</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87078431917715</v>
+        <v>99.89922258102925</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.44513872855777</v>
+        <v>84.75340906566184</v>
       </c>
       <c r="C11" t="n">
-        <v>38.81036251777544</v>
+        <v>41.62125314372467</v>
       </c>
       <c r="D11" t="n">
-        <v>1.704535541833523</v>
+        <v>1.76233313457149</v>
       </c>
       <c r="E11" t="n">
-        <v>10.05129117240398</v>
+        <v>10.71087738634164</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529883929441108</v>
+        <v>0.7472432086475319</v>
       </c>
       <c r="G11" t="n">
-        <v>26.35300655084394</v>
+        <v>28.44297952170076</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6374660754291</v>
+        <v>35.8429636117083</v>
       </c>
       <c r="I11" t="n">
-        <v>3.239673539202422</v>
+        <v>2.576742148645035</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706177455900691</v>
+        <v>4.670270054047075</v>
       </c>
       <c r="K11" t="n">
-        <v>18.55486127144223</v>
+        <v>15.24659093433818</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52693008731947</v>
+        <v>43.04635147353905</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89215387653715</v>
+        <v>99.91419555160189</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.99258725852603</v>
+        <v>82.66240426534063</v>
       </c>
       <c r="C12" t="n">
-        <v>36.85922484621636</v>
+        <v>39.93030930491871</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596656548150681</v>
+        <v>1.673719084859746</v>
       </c>
       <c r="E12" t="n">
-        <v>9.865619055066214</v>
+        <v>10.53050153347977</v>
       </c>
       <c r="F12" t="n">
-        <v>0.753847200260385</v>
+        <v>0.7478907963853233</v>
       </c>
       <c r="G12" t="n">
-        <v>24.68514116613959</v>
+        <v>27.01280292691128</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67697121197771</v>
+        <v>35.87402640820137</v>
       </c>
       <c r="I12" t="n">
-        <v>2.702807075304045</v>
+        <v>2.149146038094864</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711545001627404</v>
+        <v>4.674317477408271</v>
       </c>
       <c r="K12" t="n">
-        <v>21.00741274147397</v>
+        <v>17.33759573465938</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04337148066514</v>
+        <v>42.66051878962623</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91000906835548</v>
+        <v>99.92842382920432</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.66616649785108</v>
+        <v>83.82172067685454</v>
       </c>
       <c r="C13" t="n">
-        <v>34.95023308051191</v>
+        <v>40.89075835615635</v>
       </c>
       <c r="D13" t="n">
-        <v>1.495361308425998</v>
+        <v>1.675065139921722</v>
       </c>
       <c r="E13" t="n">
-        <v>9.61548133859467</v>
+        <v>11.17079463284396</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545861546456651</v>
+        <v>0.7484922725836807</v>
       </c>
       <c r="G13" t="n">
-        <v>23.11906404394451</v>
+        <v>27.32929188448015</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71096311370059</v>
+        <v>36.19764182733131</v>
       </c>
       <c r="I13" t="n">
-        <v>2.254547072004242</v>
+        <v>2.022358216045717</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716163466535405</v>
+        <v>4.678076703648005</v>
       </c>
       <c r="K13" t="n">
-        <v>23.33383350214894</v>
+        <v>16.17827932314544</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64085544302515</v>
+        <v>42.86360455130072</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92492202568599</v>
+        <v>99.93264223060253</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.59451480566072</v>
+        <v>81.68710664351072</v>
       </c>
       <c r="C14" t="n">
-        <v>39.27327244963017</v>
+        <v>39.06991298204758</v>
       </c>
       <c r="D14" t="n">
-        <v>1.497089191894754</v>
+        <v>1.587155911438177</v>
       </c>
       <c r="E14" t="n">
-        <v>12.01494236340373</v>
+        <v>10.86561564339738</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554580756556698</v>
+        <v>0.7490073685625569</v>
       </c>
       <c r="G14" t="n">
-        <v>25.05116291367199</v>
+        <v>25.89502111655138</v>
       </c>
       <c r="H14" t="n">
-        <v>36.6564563722365</v>
+        <v>36.22255225117002</v>
       </c>
       <c r="I14" t="n">
-        <v>2.897792915950147</v>
+        <v>1.686458298875224</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721612972847934</v>
+        <v>4.681296053515982</v>
       </c>
       <c r="K14" t="n">
-        <v>16.40548519433928</v>
+        <v>18.31289335648928</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22476074291531</v>
+        <v>42.56101704435074</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90351838688476</v>
+        <v>99.9438233828876</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.93149149359762</v>
+        <v>80.702374426243</v>
       </c>
       <c r="C15" t="n">
-        <v>39.05810047088947</v>
+        <v>38.31579633162984</v>
       </c>
       <c r="D15" t="n">
-        <v>1.472778988486238</v>
+        <v>1.545849507323805</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22270222545668</v>
+        <v>10.82212518660813</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561920442434231</v>
+        <v>0.7494515470972507</v>
       </c>
       <c r="G15" t="n">
-        <v>24.64437428053753</v>
+        <v>25.22109223591529</v>
       </c>
       <c r="H15" t="n">
-        <v>36.69207011227392</v>
+        <v>36.24403305477369</v>
       </c>
       <c r="I15" t="n">
-        <v>2.417173566078447</v>
+        <v>1.435750725167009</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726200276521393</v>
+        <v>4.684072169357818</v>
       </c>
       <c r="K15" t="n">
-        <v>17.06850850640237</v>
+        <v>19.297625573757</v>
       </c>
       <c r="L15" t="n">
-        <v>43.79289677504289</v>
+        <v>42.33874810138971</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91950575233473</v>
+        <v>99.95217000677656</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.65393499451545</v>
+        <v>78.21610818271498</v>
       </c>
       <c r="C16" t="n">
-        <v>37.15420959048592</v>
+        <v>36.05166205635634</v>
       </c>
       <c r="D16" t="n">
-        <v>1.386443623906691</v>
+        <v>1.444338325805296</v>
       </c>
       <c r="E16" t="n">
-        <v>11.84219688822735</v>
+        <v>10.31098107140804</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568220921537751</v>
+        <v>0.7498338832818898</v>
       </c>
       <c r="G16" t="n">
-        <v>23.19970331837782</v>
+        <v>23.56490069855966</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72264139674684</v>
+        <v>36.2625231164298</v>
       </c>
       <c r="I16" t="n">
-        <v>2.015989599141878</v>
+        <v>1.19706931671847</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730138075961092</v>
+        <v>4.686461770511812</v>
       </c>
       <c r="K16" t="n">
-        <v>19.34606500548454</v>
+        <v>21.78389181728501</v>
       </c>
       <c r="L16" t="n">
-        <v>43.43258169386068</v>
+        <v>42.12456416177069</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93285628983114</v>
+        <v>99.96011803541204</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.46192156665639</v>
+        <v>83.20326871056426</v>
       </c>
       <c r="C17" t="n">
-        <v>38.46223617318132</v>
+        <v>39.3150618623409</v>
       </c>
       <c r="D17" t="n">
-        <v>1.387570352882457</v>
+        <v>1.445140775259122</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65841179015761</v>
+        <v>12.05568080278455</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757437143040826</v>
+        <v>0.7502504780501301</v>
       </c>
       <c r="G17" t="n">
-        <v>23.69007420995283</v>
+        <v>25.08583257629265</v>
       </c>
       <c r="H17" t="n">
-        <v>37.22400205083918</v>
+        <v>37.79050957409885</v>
       </c>
       <c r="I17" t="n">
-        <v>2.010443875778332</v>
+        <v>1.386789016265653</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73398214400516</v>
+        <v>4.689065487813314</v>
       </c>
       <c r="K17" t="n">
-        <v>17.53807843334362</v>
+        <v>16.79673128943572</v>
       </c>
       <c r="L17" t="n">
-        <v>43.93272501468525</v>
+        <v>43.84200621595534</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93303962121018</v>
+        <v>99.95379936773197</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.25566940333364</v>
+        <v>84.76177355610199</v>
       </c>
       <c r="C18" t="n">
-        <v>36.56646964879132</v>
+        <v>40.04428524093908</v>
       </c>
       <c r="D18" t="n">
-        <v>1.307355270254854</v>
+        <v>1.446372636287556</v>
       </c>
       <c r="E18" t="n">
-        <v>12.2060550354861</v>
+        <v>12.65836679569153</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579645703795025</v>
+        <v>0.750890003514567</v>
       </c>
       <c r="G18" t="n">
-        <v>22.32055715717215</v>
+        <v>25.22279019238152</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24992229586142</v>
+        <v>37.8227228067375</v>
       </c>
       <c r="I18" t="n">
-        <v>1.676536509307732</v>
+        <v>2.167568599523282</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737278564871889</v>
+        <v>4.693062521966044</v>
       </c>
       <c r="K18" t="n">
-        <v>19.74433059666634</v>
+        <v>15.23822644389799</v>
       </c>
       <c r="L18" t="n">
-        <v>43.63335409132628</v>
+        <v>44.64529756505805</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94415433678395</v>
+        <v>99.92780924989513</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.44581590462342</v>
+        <v>81.90746973320596</v>
       </c>
       <c r="C19" t="n">
-        <v>36.01493082754178</v>
+        <v>37.52516699935737</v>
       </c>
       <c r="D19" t="n">
-        <v>1.278558308257301</v>
+        <v>1.342384945093563</v>
       </c>
       <c r="E19" t="n">
-        <v>12.17018255444862</v>
+        <v>12.04955978177668</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584091433403749</v>
+        <v>0.7514423893459348</v>
       </c>
       <c r="G19" t="n">
-        <v>21.82890484900193</v>
+        <v>23.40938495242315</v>
       </c>
       <c r="H19" t="n">
-        <v>37.27177068943349</v>
+        <v>37.85054677041314</v>
       </c>
       <c r="I19" t="n">
-        <v>1.397933214264351</v>
+        <v>1.807635960741395</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740057145877342</v>
+        <v>4.696514933412093</v>
       </c>
       <c r="K19" t="n">
-        <v>20.55418409537658</v>
+        <v>18.09253026679405</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38431461848975</v>
+        <v>44.32209249497294</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95342954140811</v>
+        <v>99.93978976112435</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.00443516613358</v>
+        <v>78.9279832605414</v>
       </c>
       <c r="C20" t="n">
-        <v>33.78883150742843</v>
+        <v>34.82434614607774</v>
       </c>
       <c r="D20" t="n">
-        <v>1.190676426426951</v>
+        <v>1.234488958716229</v>
       </c>
       <c r="E20" t="n">
-        <v>11.52791872555964</v>
+        <v>11.33228065981453</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587917837236816</v>
+        <v>0.7519207434801556</v>
       </c>
       <c r="G20" t="n">
-        <v>20.32849206060067</v>
+        <v>21.52782430980705</v>
       </c>
       <c r="H20" t="n">
-        <v>37.29057542662364</v>
+        <v>37.87464171872436</v>
       </c>
       <c r="I20" t="n">
-        <v>1.165532094925977</v>
+        <v>1.507322223248101</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742448648273009</v>
+        <v>4.699504646750974</v>
       </c>
       <c r="K20" t="n">
-        <v>22.99556483386642</v>
+        <v>21.0720167394586</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17677218053112</v>
+        <v>44.05342500444306</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96116852182598</v>
+        <v>99.9497878899794</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.69585240962429</v>
+        <v>76.03019783182427</v>
       </c>
       <c r="C21" t="n">
-        <v>37.33512171812112</v>
+        <v>32.15807955188528</v>
       </c>
       <c r="D21" t="n">
-        <v>1.191466624487922</v>
+        <v>1.130189030748247</v>
       </c>
       <c r="E21" t="n">
-        <v>13.43856548102523</v>
+        <v>10.58430069382025</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592953594919354</v>
+        <v>0.7523350566896931</v>
       </c>
       <c r="G21" t="n">
-        <v>21.97057188382492</v>
+        <v>19.70897408116246</v>
       </c>
       <c r="H21" t="n">
-        <v>38.94391221697042</v>
+        <v>37.89551089211349</v>
       </c>
       <c r="I21" t="n">
-        <v>1.646444846999275</v>
+        <v>1.25679397297955</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745595996824595</v>
+        <v>4.702094104310584</v>
       </c>
       <c r="K21" t="n">
-        <v>17.30414759037568</v>
+        <v>23.96980216817575</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30588559481191</v>
+        <v>43.83024821818208</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94515490330872</v>
+        <v>99.9581299382431</v>
       </c>
     </row>
   </sheetData>
